--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5533,6 +5533,217 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>114798770</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99795</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>569725</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6377313</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>114798416</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57251</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>569692</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6377395</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
@@ -5744,6 +5744,109 @@
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>114798546</v>
+      </c>
+      <c r="B46" t="n">
+        <v>94066</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>569731</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6377385</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5847,6 +5847,526 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>114901642</v>
+      </c>
+      <c r="B47" t="n">
+        <v>94035</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>569482</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6377259</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>114901635</v>
+      </c>
+      <c r="B48" t="n">
+        <v>90200</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>569482</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6377259</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>114901788</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57186</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>569414</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6377176</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>114902483</v>
+      </c>
+      <c r="B50" t="n">
+        <v>94035</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>569453</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6377256</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>114902641</v>
+      </c>
+      <c r="B51" t="n">
+        <v>90200</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>569449</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6377277</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6367,6 +6367,586 @@
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>114935245</v>
+      </c>
+      <c r="B52" t="n">
+        <v>90648</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Rigidoporus corticola</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>569390</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6377078</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>114935188</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5345</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>569408</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6377091</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>114935760</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57186</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>569287</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6377083</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>114934751</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5345</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>569369</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6377299</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>114935625</v>
+      </c>
+      <c r="B56" t="n">
+        <v>90440</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>569299</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6377078</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6947,6 +6947,1444 @@
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>114944032</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99805</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>569317</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6377127</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>114943983</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99805</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>569395</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6377100</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>114943921</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79550</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>569396</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6377282</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>114944054</v>
+      </c>
+      <c r="B60" t="n">
+        <v>90447</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>569293</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6377084</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Fanns på en grov granlåga</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>114944110</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99805</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>569293</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6377084</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikliga bestånd</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>114944159</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>569288</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6377092</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>114943905</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99805</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>569396</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6377282</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>114944002</v>
+      </c>
+      <c r="B64" t="n">
+        <v>90655</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Rigidoporus corticola</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>569406</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6377087</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Fanns på asplågor</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>114944137</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57186</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>569288</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6377092</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>114944026</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99805</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>569334</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6377134</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>114943936</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57252</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>569396</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6377282</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>114944016</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5345</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>569406</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6377087</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8385,6 +8385,434 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>115032649</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99818</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Väderrum, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>569376</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6377037</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>115032599</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99818</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Väderrum, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>569312</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6377117</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>115032585</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99818</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Väderrum, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>569314</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6377135</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>115032637</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99818</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Väderrum, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>569299</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6377157</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8813,6 +8813,113 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>115081908</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99818</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Gallsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>569295</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6377122</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8920,6 +8920,219 @@
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>115141471</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99818</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>569408</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6377091</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>115141668</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57189</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>569408</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6377091</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -9138,7 +9138,7 @@
         <v>115317829</v>
       </c>
       <c r="B76" t="n">
-        <v>57499</v>
+        <v>57503</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -9138,7 +9138,7 @@
         <v>115317829</v>
       </c>
       <c r="B76" t="n">
-        <v>57503</v>
+        <v>57499</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9252,6 +9252,200 @@
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131820571</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91790</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Grönhagen, Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>569579</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6377342</v>
+      </c>
+      <c r="S77" t="n">
+        <v>20</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>131816882</v>
+      </c>
+      <c r="B78" t="n">
+        <v>101243</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Grönhagen, Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>569433</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6377121</v>
+      </c>
+      <c r="S78" t="n">
+        <v>20</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -9257,7 +9257,7 @@
         <v>131820571</v>
       </c>
       <c r="B77" t="n">
-        <v>91790</v>
+        <v>91796</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>131816882</v>
       </c>
       <c r="B78" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -9257,7 +9257,7 @@
         <v>131820571</v>
       </c>
       <c r="B77" t="n">
-        <v>91847</v>
+        <v>91850</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>131816882</v>
       </c>
       <c r="B78" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106896986</v>
+        <v>109610078</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569630.2356593218</v>
+        <v>569450</v>
       </c>
       <c r="R2" t="n">
-        <v>6377356.214260948</v>
+        <v>6376804</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,31 +756,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106896987</v>
+        <v>109610230</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569811.9022954435</v>
+        <v>569443</v>
       </c>
       <c r="R3" t="n">
-        <v>6377366.310028407</v>
+        <v>6376839</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,69 +858,69 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>björk</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106896964</v>
+        <v>109610181</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>26</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Aleurocystidiellum disciforme</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(DC.) Boidin &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569552.2962326487</v>
+        <v>569462</v>
       </c>
       <c r="R4" t="n">
-        <v>6377352.195408061</v>
+        <v>6377246</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,27 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106896970</v>
+        <v>109610139</v>
       </c>
       <c r="B5" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,37 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569675.7905516836</v>
+        <v>569492</v>
       </c>
       <c r="R5" t="n">
-        <v>6377334.979934059</v>
+        <v>6376891</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,31 +1057,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>granstubbe</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109610055</v>
+        <v>109610143</v>
       </c>
       <c r="B6" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569751.77965515</v>
+        <v>570004</v>
       </c>
       <c r="R6" t="n">
-        <v>6377389.977422137</v>
+        <v>6377145</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,21 +1146,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1227,7 +1162,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>ek</t>
+          <t>granved</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1238,44 +1173,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109610200</v>
+        <v>109610144</v>
       </c>
       <c r="B7" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570036.0152219688</v>
+        <v>569293</v>
       </c>
       <c r="R7" t="n">
-        <v>6377098.461303508</v>
+        <v>6377164</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1318,21 +1248,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1344,7 +1264,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>ekstubbe</t>
+          <t>granved</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1355,44 +1275,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109610036</v>
+        <v>109610133</v>
       </c>
       <c r="B8" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>241</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569300.4022836731</v>
+        <v>569297</v>
       </c>
       <c r="R8" t="n">
-        <v>6377169.624476786</v>
+        <v>6377067</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1435,21 +1350,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1461,7 +1366,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>granved</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1472,22 +1377,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109610126</v>
+        <v>109610091</v>
       </c>
       <c r="B9" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,21 +1395,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569765.643369175</v>
+        <v>569848</v>
       </c>
       <c r="R9" t="n">
-        <v>6377397.19553711</v>
+        <v>6377350</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1552,21 +1452,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1578,7 +1468,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>alved</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1596,37 +1486,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109610185</v>
+        <v>109610200</v>
       </c>
       <c r="B10" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569708.2789903305</v>
+        <v>570036</v>
       </c>
       <c r="R10" t="n">
-        <v>6377448.294384517</v>
+        <v>6377098</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,21 +1554,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1695,7 +1570,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>ekstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1713,15 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109610189</v>
+        <v>109610112</v>
       </c>
       <c r="B11" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,21 +1599,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>530</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Dichelyma capillaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569423.4150711971</v>
+        <v>569738</v>
       </c>
       <c r="R11" t="n">
-        <v>6377180.851521857</v>
+        <v>6377401</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,21 +1656,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1809,11 +1669,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>lönn</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1823,22 +1678,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109610148</v>
+        <v>114935625</v>
       </c>
       <c r="B12" t="n">
-        <v>5295</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,43 +1696,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101728</v>
+        <v>1106</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569377.8337151597</v>
+        <v>569299</v>
       </c>
       <c r="R12" t="n">
-        <v>6377298.204425105</v>
+        <v>6377078</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1909,22 +1751,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,74 +1775,66 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>asphögstubbe</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109610015</v>
+        <v>114944054</v>
       </c>
       <c r="B13" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221235</v>
+        <v>1106</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Grönhagen, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569369.347385842</v>
+        <v>569293</v>
       </c>
       <c r="R13" t="n">
-        <v>6377291.079247111</v>
+        <v>6377083</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2027,22 +1861,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fanns på en grov granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,55 +1890,51 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109610112</v>
+        <v>109610060</v>
       </c>
       <c r="B14" t="n">
-        <v>93021</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>530</v>
+        <v>1460</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dichelyma capillaceum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(With.) Myrin</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2109,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569737.6120339755</v>
+        <v>569245</v>
       </c>
       <c r="R14" t="n">
-        <v>6377400.473177236</v>
+        <v>6377687</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2142,21 +1977,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2165,6 +1990,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2181,37 +2011,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109610188</v>
+        <v>109610061</v>
       </c>
       <c r="B15" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6457</v>
+        <v>1460</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2221,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569463.8575566364</v>
+        <v>569462</v>
       </c>
       <c r="R15" t="n">
-        <v>6377238.460385242</v>
+        <v>6377242</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2254,21 +2079,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2280,7 +2095,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>lönn</t>
+          <t>ek</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2298,37 +2113,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109610133</v>
+        <v>109610211</v>
       </c>
       <c r="B16" t="n">
-        <v>83354</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>241</v>
+        <v>1639</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2338,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569296.7620973716</v>
+        <v>569544</v>
       </c>
       <c r="R16" t="n">
-        <v>6377067.537312146</v>
+        <v>6377363</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2371,21 +2181,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2397,7 +2197,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>ek</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2415,15 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109610220</v>
+        <v>109610212</v>
       </c>
       <c r="B17" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>1639</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2455,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569557.421867925</v>
+        <v>569449</v>
       </c>
       <c r="R17" t="n">
-        <v>6377115.483491214</v>
+        <v>6377225</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2488,19 +2283,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,15 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109610216</v>
+        <v>109610027</v>
       </c>
       <c r="B18" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2668</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2567,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569543.9655874849</v>
+        <v>569360</v>
       </c>
       <c r="R18" t="n">
-        <v>6376895.624183296</v>
+        <v>6377283</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2600,21 +2380,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2623,6 +2393,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2632,22 +2407,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109610230</v>
+        <v>109610163</v>
       </c>
       <c r="B19" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2655,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>2671</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2679,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569443.7772974591</v>
+        <v>569258</v>
       </c>
       <c r="R19" t="n">
-        <v>6376839.137041656</v>
+        <v>6377605</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2712,21 +2482,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2735,11 +2495,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>björk</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2749,22 +2504,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109610224</v>
+        <v>109610165</v>
       </c>
       <c r="B20" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,21 +2522,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5321</v>
+        <v>2671</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2796,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569393.5847501776</v>
+        <v>569406</v>
       </c>
       <c r="R20" t="n">
-        <v>6377100.333448667</v>
+        <v>6377283</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2829,35 +2579,19 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>asplåga</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2867,22 +2601,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109610080</v>
+        <v>109610166</v>
       </c>
       <c r="B21" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2890,21 +2619,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>2671</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2914,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569417.6545003391</v>
+        <v>569459</v>
       </c>
       <c r="R21" t="n">
-        <v>6377171.624717415</v>
+        <v>6377251</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2947,21 +2676,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2973,7 +2692,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>lönn</t>
+          <t>ek</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2984,22 +2703,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109610034</v>
+        <v>114901642</v>
       </c>
       <c r="B22" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,34 +2721,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2818</v>
+        <v>2671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569491.8085306846</v>
+        <v>569483</v>
       </c>
       <c r="R22" t="n">
-        <v>6376893.658457917</v>
+        <v>6377259</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3061,22 +2776,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,71 +2792,62 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109610060</v>
+        <v>114902483</v>
       </c>
       <c r="B23" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1460</v>
+        <v>2671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569244.2478259249</v>
+        <v>569452</v>
       </c>
       <c r="R23" t="n">
-        <v>6377686.808435614</v>
+        <v>6377256</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3178,22 +2874,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3204,36 +2890,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>ek</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109610035</v>
+        <v>109610033</v>
       </c>
       <c r="B24" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,10 +2941,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569670.2325396581</v>
+        <v>569581</v>
       </c>
       <c r="R24" t="n">
-        <v>6377376.766405146</v>
+        <v>6377052</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3298,19 +2974,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3342,37 +3008,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109610061</v>
+        <v>109610034</v>
       </c>
       <c r="B25" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1460</v>
+        <v>2818</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3382,10 +3043,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569461.6419765975</v>
+        <v>569492</v>
       </c>
       <c r="R25" t="n">
-        <v>6377242.181246007</v>
+        <v>6376894</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3415,21 +3076,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3441,7 +3092,7 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>ek</t>
+          <t>granved</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3459,15 +3110,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109610013</v>
+        <v>109610035</v>
       </c>
       <c r="B26" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,21 +3121,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219686</v>
+        <v>2818</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3499,10 +3145,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569360.1125560795</v>
+        <v>569670</v>
       </c>
       <c r="R26" t="n">
-        <v>6377296.291204331</v>
+        <v>6377377</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3532,21 +3178,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3555,6 +3191,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3571,15 +3212,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109610187</v>
+        <v>109610036</v>
       </c>
       <c r="B27" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3587,21 +3223,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6457</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3611,10 +3247,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569457.620282116</v>
+        <v>569301</v>
       </c>
       <c r="R27" t="n">
-        <v>6377257.147360219</v>
+        <v>6377169</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3644,21 +3280,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3670,7 +3296,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>ek</t>
+          <t>granved</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3688,15 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109610181</v>
+        <v>114798546</v>
       </c>
       <c r="B28" t="n">
-        <v>90596</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3704,34 +3325,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>26</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ekskinn</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Aleurocystidiellum disciforme</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(DC.) Boidin &amp; al.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569461.5686066661</v>
+        <v>569731</v>
       </c>
       <c r="R28" t="n">
-        <v>6377246.475661864</v>
+        <v>6377384</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3758,22 +3380,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3788,27 +3400,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109610166</v>
+        <v>106896970</v>
       </c>
       <c r="B29" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3816,37 +3423,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2671</v>
+        <v>4217</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569458.796847415</v>
+        <v>569676</v>
       </c>
       <c r="R29" t="n">
-        <v>6377251.260929964</v>
+        <v>6377335</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3870,22 +3477,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3896,36 +3493,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>ek</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109610229</v>
+        <v>109610224</v>
       </c>
       <c r="B30" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3933,21 +3520,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>5321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3957,10 +3544,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569404.4443283101</v>
+        <v>569393</v>
       </c>
       <c r="R30" t="n">
-        <v>6377283.623951881</v>
+        <v>6377101</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3990,33 +3577,24 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>ek</t>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4027,22 +3605,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109610234</v>
+        <v>109610226</v>
       </c>
       <c r="B31" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,21 +3623,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>5321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4074,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569443.6363678073</v>
+        <v>569705</v>
       </c>
       <c r="R31" t="n">
-        <v>6377256.908482281</v>
+        <v>6377462</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4107,33 +3680,24 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>ek</t>
+          <t>aspved</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4151,15 +3715,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109610078</v>
+        <v>114935245</v>
       </c>
       <c r="B32" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4167,34 +3726,35 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6434</v>
+        <v>5321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569449.7706183637</v>
+        <v>569390</v>
       </c>
       <c r="R32" t="n">
-        <v>6376803.259448166</v>
+        <v>6377078</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4221,22 +3781,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4247,36 +3807,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109610012</v>
+        <v>114944002</v>
       </c>
       <c r="B33" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4284,34 +3834,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219686</v>
+        <v>5321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Grönhagen, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569334.9598626908</v>
+        <v>569405</v>
       </c>
       <c r="R33" t="n">
-        <v>6377067.651529411</v>
+        <v>6377087</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4338,22 +3891,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Fanns på asplågor</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4362,68 +3920,65 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109610027</v>
+        <v>114901564</v>
       </c>
       <c r="B34" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2668</v>
+        <v>5445</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569360.3323456061</v>
+        <v>569483</v>
       </c>
       <c r="R34" t="n">
-        <v>6377283.408102662</v>
+        <v>6377259</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4450,22 +4005,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4476,71 +4021,62 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109610217</v>
+        <v>114902641</v>
       </c>
       <c r="B35" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>5445</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569280.77060006</v>
+        <v>569450</v>
       </c>
       <c r="R35" t="n">
-        <v>6377090.354910907</v>
+        <v>6377277</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4567,22 +4103,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4597,65 +4123,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109610144</v>
+        <v>131820571</v>
       </c>
       <c r="B36" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91932</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>210</v>
+        <v>5445</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Grönhagen, Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569292.9638126008</v>
+        <v>569579</v>
       </c>
       <c r="R36" t="n">
-        <v>6377164.128016287</v>
+        <v>6377342</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4679,22 +4200,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4705,36 +4216,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>109610211</v>
+        <v>109610055</v>
       </c>
       <c r="B37" t="n">
-        <v>77706</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4742,21 +4243,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1639</v>
+        <v>6428</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4766,10 +4267,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569544.0543145228</v>
+        <v>569752</v>
       </c>
       <c r="R37" t="n">
-        <v>6377362.25635593</v>
+        <v>6377390</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4799,19 +4300,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4843,37 +4334,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>109610238</v>
+        <v>109610126</v>
       </c>
       <c r="B38" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220785</v>
+        <v>6439</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4883,10 +4369,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569513.8069928279</v>
+        <v>569766</v>
       </c>
       <c r="R38" t="n">
-        <v>6376897.256506911</v>
+        <v>6377397</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4916,21 +4402,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4939,6 +4415,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4948,22 +4429,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>109610143</v>
+        <v>109610185</v>
       </c>
       <c r="B39" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4971,21 +4447,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4995,10 +4471,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>570003.4771053054</v>
+        <v>569708</v>
       </c>
       <c r="R39" t="n">
-        <v>6377144.618021147</v>
+        <v>6377448</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5028,21 +4504,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5054,7 +4520,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>granved</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5065,22 +4531,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>109610231</v>
+        <v>109610186</v>
       </c>
       <c r="B40" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5088,21 +4549,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6457</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5112,10 +4573,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569336.5734661042</v>
+        <v>570012</v>
       </c>
       <c r="R40" t="n">
-        <v>6377067.679046144</v>
+        <v>6377154</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5145,21 +4606,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5168,11 +4619,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5182,22 +4628,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>109610139</v>
+        <v>109610187</v>
       </c>
       <c r="B41" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5205,21 +4646,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>210</v>
+        <v>6457</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5229,10 +4670,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569491.8544052204</v>
+        <v>569457</v>
       </c>
       <c r="R41" t="n">
-        <v>6376890.974216385</v>
+        <v>6377257</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5262,21 +4703,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5288,7 +4719,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>granstubbe</t>
+          <t>ek</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5299,44 +4730,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>109610113</v>
+        <v>109610188</v>
       </c>
       <c r="B42" t="n">
-        <v>73700</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6471</v>
+        <v>6457</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5346,10 +4772,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569367.104444569</v>
+        <v>569464</v>
       </c>
       <c r="R42" t="n">
-        <v>6377296.410494108</v>
+        <v>6377238</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5379,19 +4805,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5416,22 +4832,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>109610165</v>
+        <v>109610189</v>
       </c>
       <c r="B43" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5439,21 +4850,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2671</v>
+        <v>6457</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5463,10 +4874,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569406.0761740862</v>
+        <v>569424</v>
       </c>
       <c r="R43" t="n">
-        <v>6377282.577903123</v>
+        <v>6377181</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5496,21 +4907,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5519,6 +4920,11 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5528,22 +4934,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>114798770</v>
+        <v>109610229</v>
       </c>
       <c r="B44" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5551,35 +4952,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>6459</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569725</v>
+        <v>569404</v>
       </c>
       <c r="R44" t="n">
-        <v>6377313</v>
+        <v>6377284</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5606,12 +5006,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5622,67 +5022,66 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>114798416</v>
+        <v>109610231</v>
       </c>
       <c r="B45" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569691</v>
+        <v>569337</v>
       </c>
       <c r="R45" t="n">
-        <v>6377395</v>
+        <v>6377068</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5709,17 +5108,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5730,31 +5124,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>114798546</v>
+        <v>109610234</v>
       </c>
       <c r="B46" t="n">
-        <v>94179</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5762,35 +5156,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2818</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569731</v>
+        <v>569443</v>
       </c>
       <c r="R46" t="n">
-        <v>6377384</v>
+        <v>6377257</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5817,12 +5210,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5833,31 +5226,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>114902483</v>
+        <v>109610080</v>
       </c>
       <c r="B47" t="n">
-        <v>94147</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5865,35 +5258,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2671</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569452</v>
+        <v>569417</v>
       </c>
       <c r="R47" t="n">
-        <v>6377256</v>
+        <v>6377172</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5920,12 +5312,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5936,31 +5328,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>114901642</v>
+        <v>114934965</v>
       </c>
       <c r="B48" t="n">
-        <v>94147</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5968,21 +5360,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2671</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5993,10 +5385,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569483</v>
+        <v>569426</v>
       </c>
       <c r="R48" t="n">
-        <v>6377259</v>
+        <v>6377194</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6023,12 +5415,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6055,15 +5457,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>114901788</v>
+        <v>114943921</v>
       </c>
       <c r="B49" t="n">
-        <v>57215</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6071,40 +5468,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102621</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Grönhagen, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569414</v>
+        <v>569396</v>
       </c>
       <c r="R49" t="n">
-        <v>6377175</v>
+        <v>6377283</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6131,12 +5525,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6145,69 +5549,64 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>114901635</v>
+        <v>109610113</v>
       </c>
       <c r="B50" t="n">
-        <v>90292</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5445</v>
+        <v>6471</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569483</v>
+        <v>569367</v>
       </c>
       <c r="R50" t="n">
-        <v>6377259</v>
+        <v>6377296</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6234,12 +5633,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,70 +5649,69 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>lönn</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>114902641</v>
+        <v>106896964</v>
       </c>
       <c r="B51" t="n">
-        <v>90292</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5445</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569450</v>
+        <v>569553</v>
       </c>
       <c r="R51" t="n">
-        <v>6377277</v>
+        <v>6377352</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6337,12 +5735,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-02-20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-02-20</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6357,27 +5760,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>114935760</v>
+        <v>114798416</v>
       </c>
       <c r="B52" t="n">
-        <v>57215</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6385,16 +5783,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6404,21 +5802,16 @@
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569286</v>
+        <v>569691</v>
       </c>
       <c r="R52" t="n">
-        <v>6377083</v>
+        <v>6377395</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6445,22 +5838,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2024-02-22</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6487,15 +5875,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>114935245</v>
+        <v>114943936</v>
       </c>
       <c r="B53" t="n">
-        <v>90740</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6503,35 +5886,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Grönhagen, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569390</v>
+        <v>569396</v>
       </c>
       <c r="R53" t="n">
-        <v>6377078</v>
+        <v>6377283</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6563,7 +5957,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6573,7 +5967,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6588,63 +5982,69 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>114935625</v>
+        <v>115317829</v>
       </c>
       <c r="B54" t="n">
-        <v>90532</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1106</v>
+        <v>102621</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderrum, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>569299</v>
       </c>
       <c r="R54" t="n">
-        <v>6377078</v>
+        <v>6377156</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6671,22 +6071,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6701,63 +6101,69 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>114935188</v>
+        <v>114944159</v>
       </c>
       <c r="B55" t="n">
-        <v>5348</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>101728</v>
+        <v>102977</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Grönhagen, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569408</v>
+        <v>569288</v>
       </c>
       <c r="R55" t="n">
-        <v>6377090</v>
+        <v>6377091</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6789,7 +6195,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6799,12 +6205,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6819,63 +6220,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>114934751</v>
+        <v>109610012</v>
       </c>
       <c r="B56" t="n">
-        <v>5348</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>101728</v>
+        <v>219686</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569369</v>
+        <v>569335</v>
       </c>
       <c r="R56" t="n">
-        <v>6377299</v>
+        <v>6377068</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6902,27 +6297,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6937,27 +6317,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>114944110</v>
+        <v>109610013</v>
       </c>
       <c r="B57" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6965,38 +6340,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>219686</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Grönhagen, smedserum, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569293</v>
+        <v>569360</v>
       </c>
       <c r="R57" t="n">
-        <v>6377083</v>
+        <v>6377296</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7023,27 +6394,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikliga bestånd</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7052,73 +6408,63 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>114943983</v>
+        <v>109610238</v>
       </c>
       <c r="B58" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Grönhagen, smedserum, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569394</v>
+        <v>569514</v>
       </c>
       <c r="R58" t="n">
-        <v>6377101</v>
+        <v>6376897</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7145,22 +6491,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7169,72 +6505,63 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>114944002</v>
+        <v>109610015</v>
       </c>
       <c r="B59" t="n">
-        <v>90740</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5321</v>
+        <v>221235</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Grönhagen, smedserum, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569405</v>
+        <v>569369</v>
       </c>
       <c r="R59" t="n">
-        <v>6377087</v>
+        <v>6377291</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7261,27 +6588,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fanns på asplågor</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7290,34 +6602,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>114943905</v>
+        <v>106896986</v>
       </c>
       <c r="B60" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7343,23 +6649,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Grönhagen, smedserum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569396</v>
+        <v>569631</v>
       </c>
       <c r="R60" t="n">
-        <v>6377283</v>
+        <v>6377357</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7383,22 +6685,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-02-20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-02-20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7407,34 +6699,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>114944032</v>
+        <v>106896987</v>
       </c>
       <c r="B61" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7460,23 +6746,19 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Grönhagen, smedserum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569317</v>
+        <v>569812</v>
       </c>
       <c r="R61" t="n">
-        <v>6377128</v>
+        <v>6377367</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7500,22 +6782,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-02-20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-02-20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7524,34 +6796,28 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>114944159</v>
+        <v>109610216</v>
       </c>
       <c r="B62" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7559,46 +6825,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102977</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Grönhagen, smedserum, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569288</v>
+        <v>569544</v>
       </c>
       <c r="R62" t="n">
-        <v>6377091</v>
+        <v>6376895</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7625,22 +6879,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7655,65 +6899,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>114944054</v>
+        <v>109610217</v>
       </c>
       <c r="B63" t="n">
-        <v>90532</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1106</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Grönhagen, smedserum, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569293</v>
+        <v>569281</v>
       </c>
       <c r="R63" t="n">
-        <v>6377083</v>
+        <v>6377090</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7740,27 +6976,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Fanns på en grov granlåga</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7769,74 +6990,63 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>114944016</v>
+        <v>109610220</v>
       </c>
       <c r="B64" t="n">
-        <v>5348</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>101728</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Grönhagen, smedserum, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569405</v>
+        <v>569557</v>
       </c>
       <c r="R64" t="n">
-        <v>6377087</v>
+        <v>6377116</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7863,22 +7073,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7887,81 +7087,64 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>114943936</v>
+        <v>114798770</v>
       </c>
       <c r="B65" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Grönhagen, smedserum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569396</v>
+        <v>569725</v>
       </c>
       <c r="R65" t="n">
-        <v>6377283</v>
+        <v>6377313</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7988,22 +7171,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8018,27 +7191,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>114944026</v>
+        <v>114902241</v>
       </c>
       <c r="B66" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8064,20 +7232,17 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Grönhagen, smedserum, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569334</v>
+        <v>569410</v>
       </c>
       <c r="R66" t="n">
-        <v>6377134</v>
+        <v>6377189</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8104,22 +7269,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8128,34 +7283,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>114944137</v>
+        <v>114943905</v>
       </c>
       <c r="B67" t="n">
-        <v>57215</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,35 +7312,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102621</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8199,10 +7340,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569288</v>
+        <v>569396</v>
       </c>
       <c r="R67" t="n">
-        <v>6377091</v>
+        <v>6377283</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8234,7 +7375,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8244,7 +7385,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8253,6 +7394,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8271,15 +7413,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>114943921</v>
+        <v>114943983</v>
       </c>
       <c r="B68" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8287,26 +7424,27 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6464</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8314,10 +7452,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569396</v>
+        <v>569394</v>
       </c>
       <c r="R68" t="n">
-        <v>6377283</v>
+        <v>6377101</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8387,15 +7525,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>115032585</v>
+        <v>114944026</v>
       </c>
       <c r="B69" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8427,14 +7560,14 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Väderrum, smedserum, Sm</t>
+          <t>Grönhagen, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569314</v>
+        <v>569334</v>
       </c>
       <c r="R69" t="n">
-        <v>6377136</v>
+        <v>6377134</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8461,12 +7594,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8494,15 +7637,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>115032599</v>
+        <v>114944032</v>
       </c>
       <c r="B70" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8534,14 +7672,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Väderrum, smedserum, Sm</t>
+          <t>Grönhagen, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569311</v>
+        <v>569317</v>
       </c>
       <c r="R70" t="n">
-        <v>6377116</v>
+        <v>6377128</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8568,12 +7706,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8601,15 +7749,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>115032637</v>
+        <v>114944110</v>
       </c>
       <c r="B71" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8641,14 +7784,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Väderrum, smedserum, Sm</t>
+          <t>Grönhagen, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569299</v>
+        <v>569293</v>
       </c>
       <c r="R71" t="n">
-        <v>6377156</v>
+        <v>6377083</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8675,12 +7818,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikliga bestånd</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8708,15 +7866,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>115032649</v>
+        <v>115032585</v>
       </c>
       <c r="B72" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8752,10 +7905,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569376</v>
+        <v>569314</v>
       </c>
       <c r="R72" t="n">
-        <v>6377036</v>
+        <v>6377136</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8815,15 +7968,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>115081908</v>
+        <v>115032599</v>
       </c>
       <c r="B73" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8855,14 +8003,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gallsjön, Sm</t>
+          <t>Väderrum, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569295</v>
+        <v>569311</v>
       </c>
       <c r="R73" t="n">
-        <v>6377123</v>
+        <v>6377116</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8910,27 +8058,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>115141668</v>
+        <v>115032637</v>
       </c>
       <c r="B74" t="n">
-        <v>57215</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8938,43 +8081,38 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102621</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderrum, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569408</v>
+        <v>569299</v>
       </c>
       <c r="R74" t="n">
-        <v>6377090</v>
+        <v>6377156</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9001,12 +8139,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9015,33 +8153,29 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>115141471</v>
+        <v>115032649</v>
       </c>
       <c r="B75" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9067,16 +8201,20 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Grönhagen, Sm</t>
+          <t>Väderrum, smedserum, Sm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569408</v>
+        <v>569376</v>
       </c>
       <c r="R75" t="n">
-        <v>6377090</v>
+        <v>6377036</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9103,12 +8241,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9117,28 +8255,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>115317829</v>
+        <v>115081908</v>
       </c>
       <c r="B76" t="n">
-        <v>57503</v>
+        <v>101326</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9146,46 +8285,38 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102621</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Väderrum, smedserum, Sm</t>
+          <t>Gallsjön, Sm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569299</v>
+        <v>569295</v>
       </c>
       <c r="R76" t="n">
-        <v>6377156</v>
+        <v>6377123</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9212,22 +8343,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9236,66 +8357,67 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131820571</v>
+        <v>115141471</v>
       </c>
       <c r="B77" t="n">
-        <v>91850</v>
+        <v>101326</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5445</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Grönhagen, Grönhagen, Sm</t>
+          <t>Grönhagen, Sm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569579</v>
+        <v>569408</v>
       </c>
       <c r="R77" t="n">
-        <v>6377342</v>
+        <v>6377090</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9319,12 +8441,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9354,7 +8476,7 @@
         <v>131816882</v>
       </c>
       <c r="B78" t="n">
-        <v>101304</v>
+        <v>101403</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 37886-2022 artfynd.xlsx
+++ b/artfynd/A 37886-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610181</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610139</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610143</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610144</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610133</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610091</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610200</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610112</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114935625</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114944054</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,6 +1859,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610060</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610061</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610211</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2105,6 +2175,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610212</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610027</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610163</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2401,6 +2486,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610165</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2503,6 +2593,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610166</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2601,6 +2696,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114901642</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2699,6 +2799,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114902483</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2801,6 +2906,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610033</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2903,6 +3013,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610034</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3005,6 +3120,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610035</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3107,6 +3227,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610036</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3205,6 +3330,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114798546</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3302,6 +3432,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106896970</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3405,6 +3540,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610224</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3508,6 +3648,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610226</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3616,6 +3761,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114935245</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3732,6 +3882,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114944002</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3830,6 +3985,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114901564</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3928,6 +4088,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114902641</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4025,6 +4190,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131820571</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4127,6 +4297,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610055</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4229,6 +4404,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610078</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4331,6 +4511,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610126</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4433,6 +4618,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610185</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4530,6 +4720,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610186</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4632,6 +4827,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610187</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4734,6 +4934,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610188</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4836,6 +5041,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610189</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4938,6 +5148,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610229</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5040,6 +5255,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610230</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5142,6 +5362,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610231</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5244,6 +5469,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610234</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5346,6 +5576,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610080</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5454,6 +5689,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114934965</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5565,6 +5805,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943921</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5667,6 +5912,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610113</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5769,6 +6019,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106896964</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5872,6 +6127,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114798416</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5991,6 +6251,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943936</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6110,6 +6375,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115317829</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6229,6 +6499,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114944159</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6326,6 +6601,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610012</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6423,6 +6703,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610013</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6520,6 +6805,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610238</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6617,6 +6907,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610015</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6714,6 +7009,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106896986</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6811,6 +7111,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106896987</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6908,6 +7213,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610216</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7005,6 +7315,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610217</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7102,6 +7417,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610220</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7200,6 +7520,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114798770</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7298,6 +7623,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114902241</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7410,6 +7740,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943905</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7522,6 +7857,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114943983</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7634,6 +7974,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114944026</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7746,6 +8091,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114944032</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7863,6 +8213,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114944110</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7965,6 +8320,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115032585</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8067,6 +8427,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115032599</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8169,6 +8534,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115032637</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8271,6 +8641,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115032649</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8373,6 +8748,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115081908</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8470,6 +8850,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115141471</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8567,8 +8952,92 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131816882</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>